--- a/exports/trend_1d/INOXWIND_full_report.xlsx
+++ b/exports/trend_1d/INOXWIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>16.34</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42165</v>
+        <v>42166</v>
       </c>
       <c r="H2" t="n">
-        <v>100.4</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>96.91598385605008</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.09</v>
+        <v>-7.08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.65</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>14.97</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42188</v>
+        <v>42191</v>
       </c>
       <c r="H3" t="n">
-        <v>109.17</v>
+        <v>114.34</v>
       </c>
       <c r="I3" t="n">
         <v>110.6741662303992</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.41</v>
+        <v>-18.78</v>
       </c>
       <c r="L3" t="n">
-        <v>16.23</v>
+        <v>19.2</v>
       </c>
       <c r="M3" t="n">
         <v>3.15</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.46</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42219</v>
+        <v>42220</v>
       </c>
       <c r="H4" t="n">
-        <v>102.17</v>
+        <v>101.33</v>
       </c>
       <c r="I4" t="n">
         <v>101.7355885802959</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.64</v>
+        <v>-11.38</v>
       </c>
       <c r="L4" t="n">
         <v>12.15</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.44</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42292</v>
+        <v>42293</v>
       </c>
       <c r="H5" t="n">
-        <v>95.52</v>
+        <v>97.39</v>
       </c>
       <c r="I5" t="n">
         <v>96.42160289911303</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K5" t="n">
-        <v>5.73</v>
+        <v>3.89</v>
       </c>
       <c r="L5" t="n">
         <v>2.34</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42319</v>
+        <v>42321</v>
       </c>
       <c r="H6" t="n">
-        <v>92.26000000000001</v>
+        <v>88.67</v>
       </c>
       <c r="I6" t="n">
         <v>88.97004018993964</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.27</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>7.64</v>
+        <v>9.31</v>
       </c>
       <c r="M6" t="n">
         <v>3.33</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>3.89</v>
       </c>
       <c r="O6" t="n">
         <v>1.96</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.61</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H7" t="n">
-        <v>58.75</v>
+        <v>70.09</v>
       </c>
       <c r="I7" t="n">
         <v>64.6627523800141</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K7" t="n">
-        <v>33.74</v>
+        <v>20.95</v>
       </c>
       <c r="L7" t="n">
         <v>5.17</v>
@@ -840,7 +923,7 @@
         <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>19.3</v>
       </c>
       <c r="O7" t="n">
         <v>-3.89</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>26.15</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42495</v>
+        <v>42496</v>
       </c>
       <c r="H8" t="n">
-        <v>71.81</v>
+        <v>59.54</v>
       </c>
       <c r="I8" t="n">
         <v>62.06174366156971</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K8" t="n">
-        <v>2.45</v>
+        <v>-15.05</v>
       </c>
       <c r="L8" t="n">
-        <v>15.97</v>
+        <v>17.86</v>
       </c>
       <c r="M8" t="n">
         <v>2.02</v>
       </c>
       <c r="N8" t="n">
-        <v>5.24</v>
+        <v>17.09</v>
       </c>
       <c r="O8" t="n">
         <v>19.3</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>31.08</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42530</v>
+        <v>42531</v>
       </c>
       <c r="H9" t="n">
-        <v>57.47</v>
+        <v>59.44</v>
       </c>
       <c r="I9" t="n">
         <v>59.20776495202178</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.48</v>
+        <v>0.17</v>
       </c>
       <c r="L9" t="n">
         <v>22.1</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>12.57</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42584</v>
+        <v>42585</v>
       </c>
       <c r="H10" t="n">
-        <v>53.97</v>
+        <v>53.38</v>
       </c>
       <c r="I10" t="n">
         <v>53.90725291613259</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.2</v>
       </c>
       <c r="L10" t="n">
-        <v>10.11</v>
+        <v>10.45</v>
       </c>
       <c r="M10" t="n">
         <v>3.28</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.6</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42632</v>
+        <v>42633</v>
       </c>
       <c r="H11" t="n">
-        <v>48.99</v>
+        <v>49.73</v>
       </c>
       <c r="I11" t="n">
         <v>49.53253231257956</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" t="n">
-        <v>8.220000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="L11" t="n">
         <v>2.87</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>16.73</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42682</v>
+        <v>42683</v>
       </c>
       <c r="H12" t="n">
-        <v>51.26</v>
+        <v>49.68</v>
       </c>
       <c r="I12" t="n">
         <v>50.10365894380862</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K12" t="n">
-        <v>3.08</v>
+        <v>-0.1</v>
       </c>
       <c r="L12" t="n">
-        <v>5.55</v>
+        <v>15.56</v>
       </c>
       <c r="M12" t="n">
-        <v>1.32</v>
+        <v>6.26</v>
       </c>
       <c r="N12" t="n">
         <v>5.07</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.09</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42716</v>
+        <v>42717</v>
       </c>
       <c r="H13" t="n">
-        <v>49.58</v>
+        <v>50.47</v>
       </c>
       <c r="I13" t="n">
         <v>50.10403971677506</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2</v>
+        <v>-1.59</v>
       </c>
       <c r="L13" t="n">
         <v>6.74</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>11.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H14" t="n">
-        <v>45.59</v>
+        <v>44.7</v>
       </c>
       <c r="I14" t="n">
         <v>45.00458846242456</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.67</v>
+        <v>-11.43</v>
       </c>
       <c r="L14" t="n">
-        <v>11.53</v>
+        <v>12.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="N14" t="n">
         <v>2.76</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.84</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42831</v>
+        <v>42832</v>
       </c>
       <c r="H15" t="n">
-        <v>44.85</v>
+        <v>45.64</v>
       </c>
       <c r="I15" t="n">
         <v>45.32680584037421</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.34</v>
+        <v>-2.1</v>
       </c>
       <c r="L15" t="n">
         <v>9.369999999999999</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42867</v>
+        <v>42870</v>
       </c>
       <c r="H16" t="n">
-        <v>49.68</v>
+        <v>41.06</v>
       </c>
       <c r="I16" t="n">
         <v>45.13437587562809</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K16" t="n">
-        <v>8.85</v>
+        <v>-10.04</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>12.2</v>
       </c>
       <c r="M16" t="n">
-        <v>0.98</v>
+        <v>13.39</v>
       </c>
       <c r="N16" t="n">
-        <v>3.01</v>
+        <v>17.35</v>
       </c>
       <c r="O16" t="n">
         <v>1.76</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>19.83</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42928</v>
+        <v>42929</v>
       </c>
       <c r="H17" t="n">
-        <v>36.13</v>
+        <v>40.76</v>
       </c>
       <c r="I17" t="n">
         <v>37.38492252015141</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K17" t="n">
-        <v>12.01</v>
+        <v>0.73</v>
       </c>
       <c r="L17" t="n">
         <v>6.23</v>
@@ -1410,7 +1613,7 @@
         <v>1.55</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>12.81</v>
       </c>
       <c r="O17" t="n">
         <v>-17.35</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>15.21</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42935</v>
+        <v>42936</v>
       </c>
       <c r="H18" t="n">
-        <v>35.73</v>
+        <v>34.11</v>
       </c>
       <c r="I18" t="n">
         <v>35.47294033095309</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>-12.34</v>
+        <v>-16.32</v>
       </c>
       <c r="L18" t="n">
-        <v>13.91</v>
+        <v>16.68</v>
       </c>
       <c r="M18" t="n">
         <v>4.19</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>17.06</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42971</v>
+        <v>42975</v>
       </c>
       <c r="H19" t="n">
-        <v>30.31</v>
+        <v>32.23</v>
       </c>
       <c r="I19" t="n">
         <v>32.04752287794762</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K19" t="n">
-        <v>11.14</v>
+        <v>5.51</v>
       </c>
       <c r="L19" t="n">
         <v>5.92</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>20.58</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H20" t="n">
-        <v>27.8</v>
+        <v>27.01</v>
       </c>
       <c r="I20" t="n">
         <v>27.54428313778271</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" t="n">
-        <v>-13.74</v>
+        <v>-16.2</v>
       </c>
       <c r="L20" t="n">
-        <v>15.3</v>
+        <v>16.66</v>
       </c>
       <c r="M20" t="n">
         <v>0.95</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>17.28</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43034</v>
+        <v>43035</v>
       </c>
       <c r="H21" t="n">
-        <v>27.5</v>
+        <v>31.35</v>
       </c>
       <c r="I21" t="n">
         <v>30.7522343683748</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.81</v>
+        <v>-16.07</v>
       </c>
       <c r="L21" t="n">
-        <v>15.7</v>
+        <v>20.99</v>
       </c>
       <c r="M21" t="n">
         <v>2.12</v>
       </c>
       <c r="N21" t="n">
-        <v>6.51</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>-2.84</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>18.54</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43123</v>
+        <v>43124</v>
       </c>
       <c r="H22" t="n">
-        <v>33.61</v>
+        <v>32.33</v>
       </c>
       <c r="I22" t="n">
         <v>33.03547980274071</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" t="n">
-        <v>7.21</v>
+        <v>3.13</v>
       </c>
       <c r="L22" t="n">
         <v>11.8</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>13.14</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43307</v>
+        <v>43308</v>
       </c>
       <c r="H23" t="n">
-        <v>21.29</v>
+        <v>23.76</v>
       </c>
       <c r="I23" t="n">
         <v>21.4377868595489</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K23" t="n">
-        <v>34.15</v>
+        <v>26.51</v>
       </c>
       <c r="L23" t="n">
         <v>7.02</v>
@@ -1752,7 +2027,7 @@
         <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>8.85</v>
+        <v>11.6</v>
       </c>
       <c r="O23" t="n">
         <v>-3.81</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>20.35</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43369</v>
+        <v>43370</v>
       </c>
       <c r="H24" t="n">
-        <v>22.92</v>
+        <v>21.98</v>
       </c>
       <c r="I24" t="n">
         <v>22.75228446799403</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.54</v>
+        <v>-7.49</v>
       </c>
       <c r="L24" t="n">
         <v>14.73</v>
@@ -1809,7 +2096,7 @@
         <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
         <v>11.6</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>19.99</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43388</v>
+        <v>43389</v>
       </c>
       <c r="H25" t="n">
-        <v>22.28</v>
+        <v>23.46</v>
       </c>
       <c r="I25" t="n">
         <v>23.33164274803496</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.36</v>
+        <v>-6.73</v>
       </c>
       <c r="L25" t="n">
-        <v>5.37</v>
+        <v>11.87</v>
       </c>
       <c r="M25" t="n">
         <v>0.97</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>23.28</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H26" t="n">
-        <v>18.48</v>
+        <v>17.84</v>
       </c>
       <c r="I26" t="n">
         <v>18.3758214242545</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K26" t="n">
-        <v>-21.23</v>
+        <v>-23.96</v>
       </c>
       <c r="L26" t="n">
-        <v>22.25</v>
+        <v>24.98</v>
       </c>
       <c r="M26" t="n">
         <v>3.21</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>16.93</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43517</v>
+        <v>43518</v>
       </c>
       <c r="H27" t="n">
-        <v>15.62</v>
+        <v>17.79</v>
       </c>
       <c r="I27" t="n">
         <v>17.04563400560982</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K27" t="n">
-        <v>12.44</v>
+        <v>0.28</v>
       </c>
       <c r="L27" t="n">
         <v>10.26</v>
@@ -1980,7 +2303,7 @@
         <v>3.93</v>
       </c>
       <c r="N27" t="n">
-        <v>8.960000000000001</v>
+        <v>13.89</v>
       </c>
       <c r="O27" t="n">
         <v>-3.46</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>21.54</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43550</v>
+        <v>43551</v>
       </c>
       <c r="H28" t="n">
-        <v>16.46</v>
+        <v>15.87</v>
       </c>
       <c r="I28" t="n">
         <v>15.96224688046855</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.48</v>
+        <v>-10.79</v>
       </c>
       <c r="L28" t="n">
         <v>12.7</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>18.98</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H29" t="n">
-        <v>15.67</v>
+        <v>16.17</v>
       </c>
       <c r="I29" t="n">
         <v>15.97117392788838</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K29" t="n">
-        <v>1.26</v>
+        <v>-1.89</v>
       </c>
       <c r="L29" t="n">
         <v>11.47</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>15.54</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43665</v>
+        <v>43668</v>
       </c>
       <c r="H30" t="n">
-        <v>15.48</v>
+        <v>14.98</v>
       </c>
       <c r="I30" t="n">
         <v>14.98211842654859</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.27</v>
+        <v>-7.36</v>
       </c>
       <c r="L30" t="n">
-        <v>5.5</v>
+        <v>9.15</v>
       </c>
       <c r="M30" t="n">
         <v>2.67</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.27</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43794</v>
+        <v>43795</v>
       </c>
       <c r="H31" t="n">
-        <v>9.17</v>
+        <v>9.41</v>
       </c>
       <c r="I31" t="n">
         <v>9.30879858288619</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K31" t="n">
-        <v>38.79</v>
+        <v>37.18</v>
       </c>
       <c r="L31" t="n">
         <v>4.61</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>15.34</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43810</v>
+        <v>43811</v>
       </c>
       <c r="H32" t="n">
-        <v>8.48</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>8.395245805581141</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.880000000000001</v>
+        <v>-10.95</v>
       </c>
       <c r="L32" t="n">
         <v>15.2</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>33.67</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43844</v>
+        <v>43845</v>
       </c>
       <c r="H33" t="n">
-        <v>9.220000000000001</v>
+        <v>10.94</v>
       </c>
       <c r="I33" t="n">
         <v>9.769583226033443</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.02</v>
+        <v>-30.55</v>
       </c>
       <c r="L33" t="n">
-        <v>15.87</v>
+        <v>31.74</v>
       </c>
       <c r="M33" t="n">
         <v>3.46</v>
       </c>
       <c r="N33" t="n">
-        <v>6.41</v>
+        <v>18.66</v>
       </c>
       <c r="O33" t="n">
         <v>-1.18</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>22.9</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H34" t="n">
-        <v>10.15</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>9.68257344577356</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.22</v>
+        <v>-14.44</v>
       </c>
       <c r="L34" t="n">
-        <v>15.27</v>
+        <v>18.46</v>
       </c>
       <c r="M34" t="n">
         <v>2.93</v>
       </c>
       <c r="N34" t="n">
-        <v>6.97</v>
+        <v>7.78</v>
       </c>
       <c r="O34" t="n">
         <v>18.66</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>29.03</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43937</v>
+        <v>43938</v>
       </c>
       <c r="H35" t="n">
-        <v>5.87</v>
+        <v>6.41</v>
       </c>
       <c r="I35" t="n">
         <v>6.254028031888268</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K35" t="n">
-        <v>37.29</v>
+        <v>31.52</v>
       </c>
       <c r="L35" t="n">
         <v>12.71</v>
@@ -2436,7 +2855,7 @@
         <v>6.62</v>
       </c>
       <c r="N35" t="n">
-        <v>8.369999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O35" t="n">
         <v>-7.78</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>26.89</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H36" t="n">
-        <v>10.05</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>9.799306352130433</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K36" t="n">
-        <v>56.79</v>
+        <v>47.58</v>
       </c>
       <c r="L36" t="n">
         <v>9.199999999999999</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>25.22</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H37" t="n">
-        <v>9.960000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="I37" t="n">
         <v>10.48953030518006</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.29</v>
+        <v>-11.52</v>
       </c>
       <c r="L37" t="n">
-        <v>12.05</v>
+        <v>13.11</v>
       </c>
       <c r="M37" t="n">
         <v>6.96</v>
       </c>
       <c r="N37" t="n">
-        <v>5.43</v>
+        <v>5.92</v>
       </c>
       <c r="O37" t="n">
         <v>-5.87</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>21.16</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H38" t="n">
-        <v>17.3</v>
+        <v>15.77</v>
       </c>
       <c r="I38" t="n">
         <v>16.46497655583844</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K38" t="n">
-        <v>63.98</v>
+        <v>49.48</v>
       </c>
       <c r="L38" t="n">
         <v>8.91</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>25.34</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44306</v>
+        <v>44308</v>
       </c>
       <c r="H39" t="n">
-        <v>17.55</v>
+        <v>21</v>
       </c>
       <c r="I39" t="n">
         <v>19.51237621974335</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-11.29</v>
+        <v>-33.16</v>
       </c>
       <c r="L39" t="n">
-        <v>24.98</v>
+        <v>33.16</v>
       </c>
       <c r="M39" t="n">
         <v>6.93</v>
       </c>
       <c r="N39" t="n">
-        <v>6.62</v>
+        <v>19.66</v>
       </c>
       <c r="O39" t="n">
         <v>-8.84</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>29.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44433</v>
+        <v>44434</v>
       </c>
       <c r="H40" t="n">
-        <v>27.95</v>
+        <v>25.68</v>
       </c>
       <c r="I40" t="n">
         <v>26.91287484447491</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K40" t="n">
-        <v>33.1</v>
+        <v>22.29</v>
       </c>
       <c r="L40" t="n">
         <v>16.43</v>
@@ -2721,7 +3200,7 @@
         <v>3.13</v>
       </c>
       <c r="N40" t="n">
-        <v>7.32</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="O40" t="n">
         <v>19.66</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>31.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44477</v>
+        <v>44480</v>
       </c>
       <c r="H41" t="n">
-        <v>24.69</v>
+        <v>28.29</v>
       </c>
       <c r="I41" t="n">
         <v>27.35058474427502</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K41" t="n">
-        <v>3.86</v>
+        <v>-10.16</v>
       </c>
       <c r="L41" t="n">
         <v>13.24</v>
@@ -2778,7 +3269,7 @@
         <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>4.06</v>
+        <v>14.58</v>
       </c>
       <c r="O41" t="n">
         <v>-8.119999999999999</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>18.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44550</v>
+        <v>44551</v>
       </c>
       <c r="H42" t="n">
-        <v>29.47</v>
+        <v>28.59</v>
       </c>
       <c r="I42" t="n">
         <v>28.80692934775926</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K42" t="n">
-        <v>4.17</v>
+        <v>1.06</v>
       </c>
       <c r="L42" t="n">
         <v>12.37</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>23.52</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44571</v>
+        <v>44572</v>
       </c>
       <c r="H43" t="n">
-        <v>31.49</v>
+        <v>32.48</v>
       </c>
       <c r="I43" t="n">
         <v>32.13210380137717</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-10.14</v>
+        <v>-13.61</v>
       </c>
       <c r="L43" t="n">
-        <v>11.72</v>
+        <v>15.49</v>
       </c>
       <c r="M43" t="n">
         <v>1.9</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>14.99</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44613</v>
+        <v>44614</v>
       </c>
       <c r="H44" t="n">
-        <v>29.13</v>
+        <v>28.09</v>
       </c>
       <c r="I44" t="n">
         <v>28.28078393878662</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K44" t="n">
-        <v>-10.31</v>
+        <v>-13.52</v>
       </c>
       <c r="L44" t="n">
-        <v>14.25</v>
+        <v>15.02</v>
       </c>
       <c r="M44" t="n">
-        <v>2.66</v>
+        <v>3.91</v>
       </c>
       <c r="N44" t="n">
         <v>9.039999999999999</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>19.4</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44770</v>
+        <v>44771</v>
       </c>
       <c r="H45" t="n">
-        <v>21.44</v>
+        <v>21.88</v>
       </c>
       <c r="I45" t="n">
         <v>21.83957100799453</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K45" t="n">
-        <v>23.67</v>
+        <v>22.11</v>
       </c>
       <c r="L45" t="n">
         <v>10.89</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>7</v>
+      </c>
+      <c r="U45" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>15.22</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44875</v>
+        <v>44876</v>
       </c>
       <c r="H46" t="n">
-        <v>34.5</v>
+        <v>31.69</v>
       </c>
       <c r="I46" t="n">
         <v>33.02008349687722</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K46" t="n">
-        <v>57.68</v>
+        <v>44.84</v>
       </c>
       <c r="L46" t="n">
         <v>4.25</v>
@@ -3063,7 +3614,7 @@
         <v>3.24</v>
       </c>
       <c r="N46" t="n">
-        <v>8.119999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O46" t="n">
         <v>2.05</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>21.9</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44980</v>
+        <v>44981</v>
       </c>
       <c r="H47" t="n">
-        <v>25.28</v>
+        <v>26.61</v>
       </c>
       <c r="I47" t="n">
         <v>25.92636052134944</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K47" t="n">
-        <v>20.23</v>
+        <v>16.03</v>
       </c>
       <c r="L47" t="n">
         <v>10.73</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>16.21</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45000</v>
+        <v>45001</v>
       </c>
       <c r="H48" t="n">
-        <v>25.48</v>
+        <v>24.54</v>
       </c>
       <c r="I48" t="n">
         <v>24.55405261066918</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.25</v>
+        <v>-7.78</v>
       </c>
       <c r="L48" t="n">
-        <v>6.84</v>
+        <v>8.31</v>
       </c>
       <c r="M48" t="n">
         <v>0.9</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>18.61</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45048</v>
+        <v>45049</v>
       </c>
       <c r="H49" t="n">
-        <v>26.32</v>
+        <v>26.61</v>
       </c>
       <c r="I49" t="n">
         <v>26.33960589335804</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.25</v>
+        <v>-8.44</v>
       </c>
       <c r="L49" t="n">
-        <v>10.07</v>
+        <v>10.68</v>
       </c>
       <c r="M49" t="n">
         <v>1.92</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45155</v>
+        <v>45156</v>
       </c>
       <c r="H50" t="n">
-        <v>47.41</v>
+        <v>46.82</v>
       </c>
       <c r="I50" t="n">
         <v>47.08366368099125</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K50" t="n">
-        <v>78.17</v>
+        <v>75.95</v>
       </c>
       <c r="L50" t="n">
         <v>2.74</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>17.61</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45215</v>
+        <v>45216</v>
       </c>
       <c r="H51" t="n">
-        <v>50.12</v>
+        <v>54.07</v>
       </c>
       <c r="I51" t="n">
         <v>53.14927137367042</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.05</v>
+        <v>-15.48</v>
       </c>
       <c r="L51" t="n">
-        <v>14.22</v>
+        <v>19.91</v>
       </c>
       <c r="M51" t="n">
         <v>2.78</v>
       </c>
       <c r="N51" t="n">
-        <v>5.95</v>
+        <v>7.88</v>
       </c>
       <c r="O51" t="n">
         <v>-1.24</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>14.3</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H52" t="n">
-        <v>108.04</v>
+        <v>105.18</v>
       </c>
       <c r="I52" t="n">
         <v>107.0598662853495</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K52" t="n">
-        <v>99.81999999999999</v>
+        <v>94.53</v>
       </c>
       <c r="L52" t="n">
         <v>13.59</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,25 +4076,25 @@
         <v>22.48</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H53" t="n">
-        <v>125.38</v>
+        <v>131.84</v>
       </c>
       <c r="I53" t="n">
         <v>127.6844004320068</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>-19.21</v>
+        <v>-25.35</v>
       </c>
       <c r="L53" t="n">
-        <v>21.83</v>
+        <v>27.22</v>
       </c>
       <c r="M53" t="n">
-        <v>0.98</v>
+        <v>2.91</v>
       </c>
       <c r="N53" t="n">
         <v>6.83</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>17.29</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="H54" t="n">
-        <v>129.38</v>
+        <v>122.92</v>
       </c>
       <c r="I54" t="n">
         <v>128.4986248592545</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.87</v>
+        <v>-6.77</v>
       </c>
       <c r="L54" t="n">
         <v>17.23</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>20.69</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="H55" t="n">
-        <v>130.41</v>
+        <v>136.33</v>
       </c>
       <c r="I55" t="n">
         <v>135.6835873701848</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.09</v>
+        <v>-10.91</v>
       </c>
       <c r="L55" t="n">
-        <v>12.07</v>
+        <v>16.04</v>
       </c>
       <c r="M55" t="n">
-        <v>2.16</v>
+        <v>2.57</v>
       </c>
       <c r="N55" t="n">
         <v>5</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>16.17</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="H56" t="n">
-        <v>136.82</v>
+        <v>133.76</v>
       </c>
       <c r="I56" t="n">
         <v>134.8590670051444</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>0.36</v>
+        <v>-1.89</v>
       </c>
       <c r="L56" t="n">
         <v>5.68</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>20.25</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45435</v>
+        <v>45436</v>
       </c>
       <c r="H57" t="n">
-        <v>149.14</v>
+        <v>162.65</v>
       </c>
       <c r="I57" t="n">
         <v>157.4493097202549</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.5</v>
+        <v>-21.6</v>
       </c>
       <c r="L57" t="n">
-        <v>18.28</v>
+        <v>22.63</v>
       </c>
       <c r="M57" t="n">
-        <v>2.3</v>
+        <v>5.75</v>
       </c>
       <c r="N57" t="n">
         <v>9.119999999999999</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>17.48</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H58" t="n">
-        <v>151.16</v>
+        <v>136.08</v>
       </c>
       <c r="I58" t="n">
         <v>139.7121776570818</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-7.06</v>
+        <v>-16.34</v>
       </c>
       <c r="L58" t="n">
         <v>19.4</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>27.59</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45484</v>
+        <v>45485</v>
       </c>
       <c r="H59" t="n">
-        <v>155.84</v>
+        <v>169.3</v>
       </c>
       <c r="I59" t="n">
         <v>158.0148056188902</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K59" t="n">
-        <v>-14.52</v>
+        <v>-24.41</v>
       </c>
       <c r="L59" t="n">
-        <v>22.35</v>
+        <v>26.76</v>
       </c>
       <c r="M59" t="n">
         <v>4.47</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>17.74</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H60" t="n">
-        <v>219.08</v>
+        <v>205.17</v>
       </c>
       <c r="I60" t="n">
         <v>213.2641283505736</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K60" t="n">
-        <v>29.4</v>
+        <v>21.19</v>
       </c>
       <c r="L60" t="n">
         <v>18.43</v>
@@ -3861,7 +4580,7 @@
         <v>4.11</v>
       </c>
       <c r="N60" t="n">
-        <v>4.97</v>
+        <v>6.35</v>
       </c>
       <c r="O60" t="n">
         <v>8.640000000000001</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>21.6</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45685</v>
+        <v>45686</v>
       </c>
       <c r="H61" t="n">
-        <v>133</v>
+        <v>159.2</v>
       </c>
       <c r="I61" t="n">
         <v>157.3405433578923</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K61" t="n">
-        <v>35.18</v>
+        <v>22.41</v>
       </c>
       <c r="L61" t="n">
         <v>10.93</v>
@@ -3918,7 +4649,7 @@
         <v>5</v>
       </c>
       <c r="N61" t="n">
-        <v>5.41</v>
+        <v>19.7</v>
       </c>
       <c r="O61" t="n">
         <v>-6.35</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>26.32</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45716</v>
+        <v>45719</v>
       </c>
       <c r="H62" t="n">
-        <v>148.05</v>
+        <v>141.88</v>
       </c>
       <c r="I62" t="n">
         <v>145.6140317130677</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K62" t="n">
-        <v>-7</v>
+        <v>-10.88</v>
       </c>
       <c r="L62" t="n">
-        <v>14.77</v>
+        <v>15.48</v>
       </c>
       <c r="M62" t="n">
         <v>3.02</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>21.55</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H63" t="n">
-        <v>165.07</v>
+        <v>166.54</v>
       </c>
       <c r="I63" t="n">
         <v>165.404851614157</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.34</v>
+        <v>-17.38</v>
       </c>
       <c r="L63" t="n">
         <v>22.77</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>14.56</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="H64" t="n">
-        <v>174.02</v>
+        <v>170</v>
       </c>
       <c r="I64" t="n">
         <v>171.2142310638423</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K64" t="n">
-        <v>4.49</v>
+        <v>2.08</v>
       </c>
       <c r="L64" t="n">
         <v>9.050000000000001</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>11.8</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="H65" t="n">
-        <v>148.92</v>
+        <v>151.32</v>
       </c>
       <c r="I65" t="n">
         <v>150.6165029321505</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K65" t="n">
-        <v>12.4</v>
+        <v>10.99</v>
       </c>
       <c r="L65" t="n">
         <v>4.95</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.45</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H66" t="n">
-        <v>144.31</v>
+        <v>141.14</v>
       </c>
       <c r="I66" t="n">
         <v>141.8705823019452</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.63</v>
+        <v>-6.73</v>
       </c>
       <c r="L66" t="n">
-        <v>4.82</v>
+        <v>6.94</v>
       </c>
       <c r="M66" t="n">
         <v>0.09</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>10.9</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H67" t="n">
-        <v>149.15</v>
+        <v>152.21</v>
       </c>
       <c r="I67" t="n">
         <v>152.0307339792079</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.68</v>
+        <v>-7.84</v>
       </c>
       <c r="L67" t="n">
-        <v>7.94</v>
+        <v>9.91</v>
       </c>
       <c r="M67" t="n">
         <v>0.8</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>8.1</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="H68" t="n">
-        <v>146.11</v>
+        <v>140.92</v>
       </c>
       <c r="I68" t="n">
         <v>145.0150436570406</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.01</v>
+        <v>-7.42</v>
       </c>
       <c r="L68" t="n">
-        <v>5.65</v>
+        <v>7.61</v>
       </c>
       <c r="M68" t="n">
         <v>1.04</v>
       </c>
       <c r="N68" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="O68" t="n">
         <v>2.05</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>12.25</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H69" t="n">
-        <v>87.55</v>
+        <v>93.41</v>
       </c>
       <c r="I69" t="n">
         <v>89.74339397124906</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K69" t="n">
-        <v>37.87</v>
+        <v>33.71</v>
       </c>
       <c r="L69" t="n">
         <v>3.92</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>6</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>16.77</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="H70" t="n">
-        <v>95.81</v>
+        <v>93.02</v>
       </c>
       <c r="I70" t="n">
         <v>93.84057673140262</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K70" t="n">
-        <v>2.57</v>
+        <v>-0.42</v>
       </c>
       <c r="L70" t="n">
         <v>4.69</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>13.7</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H71" t="n">
-        <v>74.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I71" t="n">
         <v>75.55434955939285</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K71" t="n">
-        <v>20.02</v>
+        <v>18.73</v>
       </c>
       <c r="L71" t="n">
         <v>4.05</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>10.32</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="H72" t="n">
-        <v>71.5</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="I72" t="n">
         <v>71.43784315906296</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.42</v>
+        <v>-8.06</v>
       </c>
       <c r="L72" t="n">
-        <v>6.65</v>
+        <v>8.06</v>
       </c>
       <c r="M72" t="n">
         <v>1.56</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>19</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9461,7 +10344,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.3</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="6">
@@ -9471,7 +10354,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9481,7 +10364,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
@@ -9491,7 +10374,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9501,7 +10384,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.5</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="10">
@@ -9511,7 +10394,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -9521,7 +10404,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -9531,7 +10414,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -9541,7 +10424,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.4</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="14">
@@ -9551,7 +10434,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.05</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="15">
@@ -9561,7 +10444,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.06</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="16">
@@ -9571,7 +10454,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.01</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="17">
@@ -9581,7 +10464,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99.81999999999999</v>
+        <v>94.53</v>
       </c>
     </row>
     <row r="18">
@@ -9591,7 +10474,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.9</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="19">
@@ -9601,7 +10484,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11.15</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="20">
@@ -9611,7 +10494,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10.93</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="21">
@@ -9621,7 +10504,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24.98</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="22">
@@ -9631,7 +10514,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -9641,7 +10524,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
@@ -9651,7 +10534,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.24</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="25">
@@ -9661,7 +10544,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.83</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="26">
@@ -9671,7 +10554,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.77</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -9691,7 +10574,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
